--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_06_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_06_19_Cau.xlsx
@@ -677,7 +677,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ kết luận thuộc tính được đo trực tiếp; hãy liệt kê các siêu dữ liệu còn thiếu.</t>
+          <t>Con số công bố `Model X: 300B total parameters` chỉ cho biết quy mô tổng số tham số; nếu là kiến trúc MoE (Mixture of Experts) thì số tham số hoạt động ở mỗi token thấp hơn nhiều, nên chưa đủ dữ kiện để suy ra năng lực tính toán mỗi token hay độ trễ phục vụ.</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp dụng ngưỡng trước, rồi mới tối ưu chỉ số phụ như chi phí.</t>
+          <t>Tiêu chí ưu tiên hàng đầu là độ chính xác thực tế với ngưỡng bắt buộc 92%. Model F chỉ đạt 88% nên bị loại trực tiếp; Model E đạt 94% vượt ngưỡng nên được chọn dù chi phí cao hơn.</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt file cấu hình mẫu với file chứa credential thật, rồi kiểm tra cách xử lý khi biến môi trường không tồn tại.</t>
+          <t>Thực hành an toàn cấu hình: Xóa secret hard-code khỏi source (a), Bỏ track .env và thêm vào .gitignore (b), Giữ .env.example mẫu không có secret thật (c), và Báo lỗi cấu hình rõ ràng trước khi gọi mạng (e). In key ra log (d) là lỗ hổng rò rỉ credential.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách lỗi cấu hình cục bộ khỏi lỗi do server trả sau lời gọi mạng.</t>
+          <t>Khi `os.getenv('API_KEY')` trả về `None`, cách xử lý đúng là kiểm tra ngay sau khi nạp cấu hình và ném lỗi rõ ràng trước khi thực hiện network call, thay vì gửi đi request lỗi xác thực mơ hồ.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu từng trường với chữ ký hàm được cung cấp; không dùng trí nhớ về SDK khác.</t>
+          <t>Lệnh gọi đúng contract phải truyền đúng các trường: model='m1', messages gồm system message trước rồi đến user message, temperature=0.2 và max_output_tokens=200.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So cả tên trường lẫn ý nghĩa/giá trị được đặt vào trường đó.</t>
+          <t>Lệnh gọi bị các lỗi: Đặt nhầm content vào role đối nghịch (a), Message order đưa user trước system (b), Tráo giá trị temperature=200 và max_tokens=0.2 (c), trong khi tên phương thức `client.chat.create` vẫn đúng contract (e).</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đi theo cấu trúc choice → message → content.</t>
+          <t>Cấu trúc phản hồi là dict lồng nhau: để lấy văn bản được sinh từ `{'choices':[{'message':{'content':'Xin chào'}}]}`, biểu thức truy xuất chính xác là `response['choices'][0]['message']['content']`.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tên có chữ `output` không đồng nghĩa trường đó chứa văn bản output.</t>
+          <t>Các trường `input_tokens=80`, `output_tokens=20` và `total_tokens=100` đều là các trường số liệu thống kê việc sử dụng token (usage metrics) của request, không chứa nội dung văn bản.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_06_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_06_19_Cau.xlsx
@@ -626,10 +626,18 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách số tham số được lưu khỏi số tham số đi qua phép tính ở mỗi token.
-Phân tích theo nguyên lý thiết kế: Tách số tham số được lưu khỏi số tham số đi qua phép tính ở mỗi token.</t>
+- Phân biệt total và active parameters (1.5 điểm): Định nghĩa chính xác tổng tham số lưu trữ trong VRAM so với tham số thực tế tính toán trên mỗi token.
+- Giải thích lượng tính toán thực tế (1.5 điểm): Chứng minh M kích hoạt 10B tham số nên FLOPs thực tế chỉ bằng 1/2 của D (20B), bác bỏ suy luận gấp 4 lần.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân biệt tổng số tham số và tham số hoạt động:
+- Tổng số tham số (`total parameters`): Là toàn bộ trọng số của mô hình được lưu trữ trong bộ nhớ VRAM của GPU (ví dụ Model D có 20B, Model M có 80B tham số).
+- Số tham số hoạt động (`active parameters`): Là lượng tham số thực tế tham gia vào các phép tính nhân ma trận (FLOPs) trong lượt tính toán (forward pass) cho một token đơn lẻ tại runtime (Model D kích hoạt toàn bộ 20B, trong khi Model M qua bộ định tuyến router chỉ kích hoạt 10B).
+2. Giải thích vì sao không thể kết luận M tốn lượng tính toán gấp 4:
+Khối lượng tính toán (FLOPs) và độ trễ sinh token tỷ lệ thuận trực tiếp với số tham số hoạt động (active parameters) trên mỗi token, chứ không phụ thuộc vào tổng tham số lưu trữ. Vì Model M chỉ kích hoạt 10B tham số hoạt động cho mỗi token, lượng tính toán thực tế của M chỉ bằng một nửa (1/2) so với Model D (kích hoạt 20B tham số hoạt động), mặc dù tổng dung lượng trọng số lưu trữ của M lớn gấp 4 lần D.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kiến trúc Mixture of Experts (MoE) áp dụng nguyên lý tính toán thưa (Conditional Computation / Sparsity). Bằng cách chỉ kích hoạt một tập con các chuyên gia (experts) cho mỗi token, MoE đạt được sức chứa tri thức khổng lồ (tổng dung lượng tham số lớn) nhưng vẫn duy trì chi phí tính toán (FLOPs per token) tương đương với một mô hình dày (dense) cỡ nhỏ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Shazeer, N., et al. (2017). Outrageously Large Neural Networks: The Sparsely-Gated Mixture-of-Experts Layer. ICLR 2017. https://arxiv.org/abs/1701.06538; Fedus, W., et al. (2022). Switch Transformers. JMLR.</t>
         </is>
       </c>
     </row>
@@ -713,10 +721,19 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Loại model vi phạm tiêu chí bắt buộc trước khi so sánh độ trễ.
-Phân tích theo nguyên lý thiết kế: Loại model vi phạm tiêu chí bắt buộc trước khi so sánh độ trễ.</t>
+- Chọn đúng Model A (1.0 điểm): Lựa chọn chính xác Model A.
+- Phân tích vi phạm tiêu chí bắt buộc (1.0 điểm): Chỉ ra Model B vi phạm tiêu chí đủ 4 trường với tỷ lệ lỗi 30%, không thể triển khai production.
+- Giải thích thứ bậc ưu tiên độ trễ (1.0 điểm): Nêu rõ độ trễ chỉ được tối ưu hóa sau khi các tiêu chí hợp lệ cấu trúc đã đạt 100%.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Quyết định chọn model: Chọn MODEL A.
+- Giải thích chi tiết theo thứ tự ưu tiên:
+1. Tiêu chí 1 (JSON hợp lệ) và Tiêu chí 2 (Đủ 4 trường) là các ràng buộc cứng bắt buộc (hard constraints / pass-fail criteria). Hệ thống yêu cầu đầu ra có cấu trúc để các dịch vụ downstream xử lý tự động; việc thiếu trường sẽ dẫn đến lỗi hệ thống (runtime schema validation crash).
+2. Model A đạt tuyệt đối 10/10 JSON hợp lệ và 10/10 đủ 4 trường (tỷ lệ thành công 100%). Ngược lại, Model B thất bại ở tiêu chí bắt buộc khi chỉ đạt 7/10 đủ trường (tỷ lệ lỗi lên tới 30%).
+3. Tiêu chí 3 (độ trễ) chỉ được xem xét sau khi các mô hình đã vượt qua toàn bộ các tiêu chí bắt buộc. Mặc dù Model B có thời gian trung vị nhanh hơn (1,1 giây so với 1,8 giây), sự vượt trội về tốc độ hoàn toàn vô nghĩa khi độ tin cậy của dữ liệu đầu ra không được bảo đảm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc thiết kế hệ thống theo mức độ nghiêm ngặt (Lexicographic Optimization) quy định: Tính đúng đắn của dữ liệu (Data Integrity &amp; Correctness) luôn luôn đứng trên Tốc độ (Latency). Không bao giờ được đánh đổi tỷ lệ lỗi định dạng cấu trúc 30% lấy 0,7 giây độ trễ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Service Level Objectives and Error Budgets (https://sre.google/sre-book/service-level-objectives/); Martin Fowler - Structural Interface Contracts.</t>
         </is>
       </c>
     </row>
@@ -747,10 +764,19 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi chỉ số nào thực sự phân biệt hai model vượt qua nhiễu đo.
-Phân tích theo nguyên lý thiết kế: Hỏi chỉ số nào thực sự phân biệt hai model vượt qua nhiễu đo.</t>
+- Khẳng định không tuyên bố thắng (1.0 điểm): Nêu rõ không thể chọn người thắng vì điểm bằng nhau và latency chênh lệch nằm trong biên độ nhiễu.
+- Bổ sung tiêu chí chi phí (1.0 điểm): Yêu cầu đo lường cụ thể chi phí token / tài nguyên phần cứng.
+- Đề xuất phương pháp thống kê và ca biên (1.0 điểm): Nêu bước tăng cỡ mẫu, kiểm định ý nghĩa thống kê và kiểm thử stress test.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Có nên tuyên bố model thắng không?: KHÔNG NÊN tuyên bố model nào chiến thắng ở thời điểm này. Cả hai mô hình đều có cùng điểm chất lượng (18/20), sự chênh lệch về độ trễ nằm trong khoảng phương sai sai số ngẫu nhiên (measurement noise), và biến số then chốt về chi phí vận hành vẫn chưa được thu thập.
+- Bước tiếp theo cần thực hiện:
+1. Thu thập và định lượng chỉ số chi phí: Đo lường chính xác lượng token tiêu thụ và chi phí API / VRAM tương ứng của từng mô hình trên mỗi request.
+2. Mở rộng kích thước mẫu và kiểm định thống kê: Tăng số lượng mẫu đánh giá và áp dụng kiểm định thống kê (ví dụ: t-test hoặc bootstrap confidence intervals) để xác định xem sự khác biệt giữa hai mô hình có ý nghĩa thống kê (statistical significance, $p &lt; 0.05$) hay chỉ là ngẫu nhiên.
+3. Thử nghiệm trên các trường hợp biên (Stress / Edge cases): Đưa vào các prompt phức tạp, câu hỏi đa nghĩa để tìm ra điểm gãy của từng mô hình.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong đánh giá kỹ thuật (Empirical Evaluation), việc vội vàng đưa ra quyết định khi số liệu chưa đạt ý nghĩa thống kê và thiếu khía cạnh chi phí sẽ dẫn đến các quyết định kiến trúc sai lầm. Cần kiểm soát biến gây nhiễu và hoàn thiện bức tranh ROI toàn diện.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kohavi, R., et al. (2020). Trustworthy Online Controlled Experiments: A Practical Guide to A/B Testing. Cambridge University Press. https://exp-platform.com/; Stanford HELM (https://crfm.stanford.edu/helm/)</t>
         </is>
       </c>
     </row>
@@ -830,10 +856,18 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So từng khía cạnh của benchmark với workload thật: ngôn ngữ, lĩnh vực, cách tương tác và chỉ số.
-Phân tích theo nguyên lý thiết kế: So từng khía cạnh của benchmark với workload thật: ngôn ngữ, lĩnh vực, cách tương tác và chỉ số.</t>
+- Nêu 2 khoảng trống hiệu lực (2.0 điểm): Chỉ ra đúng khoảng cách ngôn ngữ/pháp luật Việt Nam và sự lệch pha giữa trắc nghiệm đóng với tư vấn pháp lý mở.
+- Nêu bằng chứng cần bổ sung (1.0 điểm): Đề xuất xây dựng benchmark pháp lý tiếng Việt và đánh giá từ chuyên gia pháp luật độc lập.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hai khoảng trống về hiệu lực (Validity Gaps):
+- Khoảng trống về ngôn ngữ và thể chế pháp lý: Benchmark tiếng Anh (như MMLU) đo lường khả năng xử lý ngữ pháp tiếng Anh và hệ thống pháp luật thông luật (Common Law), hoàn toàn không phản ánh được năng lực am hiểu văn phong hành chính, cấu trúc ngữ pháp phức tạp và hệ thống văn bản quy phạm pháp luật Dân luật (Civil Law) của Việt Nam.
+- Khoảng trống về hình thức tác vụ (Task Modality Mismatch): Câu hỏi trắc nghiệm (Multiple-Choice Questions) chỉ đo lường khả năng nhận diện xác suất trong tập lựa chọn đóng, trong khi chatbot pháp lý thực tế đòi hỏi sinh ngôn ngữ tự do, tư vấn đa lượt (multi-turn), tổng hợp ngữ cảnh và trích dẫn điều khoản chính xác.
+2. Bằng chứng cần bổ sung:
+Cần xây dựng bộ dữ liệu đánh giá miền pháp lý Việt Nam chuyên biệt (Vietnamese Legal Benchmark) gồm các câu hỏi tình huống thực tế, kèm sự thẩm định trực tiếp của các luật sư/chuyên gia pháp lý (Human-in-the-loop expert evaluation) về tính chính xác của trích dẫn và lập luận pháp lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Construct Validity' trong đo lường phần mềm chỉ ra rằng một chỉ số benchmark chỉ có giá trị khi nó đo lường đúng năng lực cần thiết trong môi trường tác nghiệp thực tế. Việc ngoại suy từ benchmark trắc nghiệm tổng quát sang ứng dụng chuyên ngành có rủi ro pháp lý cao là một sai lầm nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Wang, A., et al. (2019). SuperGLUE: A Stickier Benchmark for General-Purpose Language Understanding Systems. NeurIPS 2019. https://arxiv.org/abs/1905.00537; HELM Legal Benchmarking.</t>
         </is>
       </c>
     </row>
@@ -914,10 +948,18 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi model có thể đã thấy chính câu hỏi hoặc đáp án trước bài đánh giá hay không.
-Phân tích theo nguyên lý thiết kế: Hỏi model có thể đã thấy chính câu hỏi hoặc đáp án trước bài đánh giá hay không.</t>
+- Giải thích tác động của rò rỉ dữ liệu (1.5 điểm): Nêu rõ hiện tượng data contamination dẫn đến học vẹt (memorization) thay vì năng lực tổng quát hóa thật sự.
+- Đề xuất phương pháp kiểm tra (1.5 điểm): Đưa ra giải pháp tạo tập benchmark ẩn mới (canary dataset) hoặc hoán đổi dữ liệu (perturbation testing).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Vì sao nghi ngờ rò rỉ dữ liệu làm nhận định yếu đi:
+Hiện tượng rò rỉ dữ liệu (Data Contamination / Benchmark Leakage) xảy ra khi câu hỏi và đáp án của benchmark công khai bị thu thập vào tập dữ liệu tiền huấn luyện (pretraining corpus) của mô hình. Khi đó, điểm số gần như tuyệt đối chỉ phản ánh khả năng học vẹt và ghi nhớ nguyên văn (verbatim memorization/overfitting), chứ không hề chứng minh được năng lực suy luận tổng quát hóa (generalization) trên dữ liệu mới chưa từng thấy trong thực tế.
+2. Đề xuất cách kiểm tra bổ sung:
+- Tạo tập benchmark ẩn mới (private canary dataset / out-of-distribution eval) gồm các câu hỏi mới được soạn thảo độc quyền sau ngày mô hình cutoff.
+- Thực hiện biến đổi dữ liệu kiểm thử (perturbation testing): Giữ nguyên cấu trúc logic nhưng thay đổi tên thực thể, số liệu và cách diễn đạt trong các câu hỏi cũ để đo lường xem mô hình có thực sự suy luận hay chỉ dựa vào việc khớp mẫu từ vựng đã học thuộc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Goodhart's Law: 'Khi một thước đo trở thành mục tiêu, nó không còn là một thước đo tốt nữa'. Hiện tượng Data Contamination làm xói mòn tính khách quan của các benchmark công khai, buộc các kỹ sư hệ thống phải thiết lập các bộ test nội bộ được bảo mật chặt chẽ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jacovi, A., et al. (2023). Stop Uploading Test Data to the Internet: When Benchmarks Become Training Data. arXiv:2305.10160. https://arxiv.org/abs/2305.10160; OpenAI GPT-4 Technical Report.</t>
         </is>
       </c>
     </row>
@@ -1049,10 +1091,18 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kho mã chỉ cần contract về tên biến, không cần giá trị thật.
-Phân tích theo nguyên lý thiết kế: Kho mã chỉ cần contract về tên biến, không cần giá trị thật.</t>
+- Vị trí lưu key thật và cách code lấy (1.5 điểm): Nêu rõ key lưu ở `.env` cục bộ và lấy qua biến môi trường (`os.getenv`).
+- File mẫu và file bỏ theo dõi (1.5 điểm): Nêu đúng file mẫu `.env.example` lưu trên Git và file `.env` phải đưa vào `.gitignore`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Cấu hình tối thiểu chuẩn cho phát triển cục bộ:
+1. Key thật nằm ở đâu: Lưu trữ trong file môi trường bí mật tại máy cục bộ (file `.env` hoặc trong hệ thống quản lý Secret/Keychain của hệ điều hành), tuyệt đối không nhúng trực tiếp vào mã nguồn (hardcode).
+2. Code lấy bằng cách nào: Code nạp giá trị thông qua biến môi trường hệ thống, ví dụ sử dụng `os.getenv('OPENAI_API_KEY')` trong Python hoặc thư viện `dotenv`.
+3. Kho mã giữ file mẫu nào: Kho mã (Git repository) lưu file mẫu `.env.example` mô tả hợp đồng danh sách tên biến môi trường cần thiết kèm giá trị rỗng hoặc giá trị giả định mẫu.
+4. File nào phải bỏ theo dõi: File chứa key thật (`.env`, `.env.local`) bắt buộc phải được khai báo trong file `.gitignore` để Git không bao giờ theo dõi hay commit lên repository.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc III trong kiến trúc The Twelve-Factor App quy định: Tách biệt cấu hình và bí mật khỏi mã nguồn (Config in the Environment). Việc để lộ API key trong Git commit history là một trong những lỗ hổng bảo mật phổ biến nhất dẫn đến chiếm đoạt tài khoản và rò rỉ dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+The Twelve-Factor App - III. Config (https://12factor.net/config); OWASP Secrets Management Cheat Sheet.</t>
         </is>
       </c>
     </row>
@@ -1208,10 +1258,17 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tên khái niệm giống nhau không đảm bảo tên trường giống nhau giữa các SDK/provider.
-Phân tích theo nguyên lý thiết kế: Tên khái niệm giống nhau không đảm bảo tên trường giống nhau giữa các SDK/provider.</t>
+- Nêu đúng sửa đổi (1.5 điểm): Đổi chính xác trường `max_tokens` thành `max_output_tokens` theo API contract.
+- Giải thích vì sao không đoán alias (1.5 điểm): Phân tích nguy cơ bị từ chối request (422/400) hoặc bị lờ đi âm thầm khiến hệ thống dùng giá trị mặc định sai lệch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa đổi cần làm: Đổi tên trường trong payload JSON request từ `max_tokens` thành `max_output_tokens` để tuân thủ chính xác hợp đồng quy định của nhà cung cấp.
+2. Vì sao không nên đoán alias sẽ hoạt động:
+- Các API hiện đại thường sử dụng schema validator nghiêm ngặt (như Pydantic hoặc JSON Schema). Việc gửi trường không có trong đặc tả kỹ thuật sẽ dẫn đến lỗi HTTP 422 Unprocessable Entity hoặc HTTP 400 Bad Request.
+- Trong trường hợp API không báo lỗi, trường không xác định thường bị âm thầm bỏ qua (silently ignored). Khi đó, mô hình sẽ tự động áp dụng giá trị mặc định (default limit), có thể gây cắt cụt văn bản đột ngột hoặc sinh thừa token gây lãng phí chi phí mà lập trình viên không hề hay biết.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Strict Interface Adherence' trong kiến trúc RESTful API đòi hỏi hệ thống client phải tuân thủ nghiêm ngặt hợp đồng giao diện. Giả định ngầm định về bí danh (alias assumption) là nguồn cơn của các lỗi âm thầm (silent failures) rất khó debug trong môi trường production.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAPI Specification 3.0 (https://spec.openapis.org/oas/v3.0.3); Postel's Law / Robustness Principle in Software Engineering.</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1343,23 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách trạng thái `không có nội dung` khỏi trường hợp nội dung là chuỗi rỗng hợp lệ nếu contract cho phép.
-Phân tích theo nguyên lý thiết kế: Tách trạng thái `không có nội dung` khỏi trường hợp nội dung là chuỗi rỗng hợp lệ nếu contract cho phép.</t>
+- Kiểm tra mảng phòng thủ (1.5 điểm): Viết điều kiện kiểm tra `if not choices` trước khi truy cập index 0 để ngăn chặn `IndexError`.
+- Xử lý lỗi minh bạch không bịa đặt (1.5 điểm): Ném ngoại lệ có cấu trúc hoặc trả về mã lỗi rõ ràng báo hiệu phản hồi rỗng/bị chặn an toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Cách xử lý chủ động không làm crash ứng dụng và không bịa nội dung:
+1. Kiểm tra điều kiện tiên quyết (Defensive Guard Check): Trước khi truy cập `choices[0]`, kiểm tra độ dài mảng:
+```python
+choices = response.get('choices', [])
+if not choices:
+    # Kiểm tra cờ từ chối do an toàn nếu có
+    prompt_filter = response.get('prompt_filter_results', [])
+    raise ValueError(f'API returned empty choices list. Safety filters triggered: {prompt_filter}')
+```
+2. Xử lý phản hồi có cấu trúc: Trả về một đối tượng lỗi có kiểm soát (Error Result Object) hoặc thông báo rõ ràng cho người dùng rằng yêu cầu không tạo ra nội dung do bị bộ lọc an toàn của nhà cung cấp chặn hoặc do sự cố kỹ thuật từ phía server, thay vì trả về một chuỗi bịa đặt hay để phát sinh ngoại lệ `IndexError`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Lập trình phòng thủ (Defensive Programming) đòi hỏi mọi thao tác truy cập chỉ mục mảng từ dữ liệu mạng đều phải được bọc bởi guard clause. Tách biệt rõ ràng giữa 'kết quả rỗng hợp lệ' và 'sự cố bị chặn bởi bộ lọc' giúp hệ thống duy trì tính ổn định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI API Reference - Errors and Safety Filter Responses; Fowler, M. - Refactoring: Guard Clauses (https://refactoring.com).</t>
         </is>
       </c>
     </row>
@@ -1364,10 +1434,18 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Provider này dùng `prompt` cho đầu vào và `completion` cho phần output được sinh.
-Phân tích theo nguyên lý thiết kế: Provider này dùng `prompt` cho đầu vào và `completion` cho phần output được sinh.</t>
+- Báo cáo token đầu vào (1.0 điểm): Xác định đúng 120 token từ `prompt_tokens`.
+- Báo cáo token đầu ra (1.0 điểm): Xác định đúng 30 token từ `completion_tokens`.
+- Báo cáo tổng token (1.0 điểm): Xác định đúng 150 token từ `total_tokens`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Báo cáo số token chính xác theo đúng ý nghĩa của từng trường trong hợp đồng dữ liệu:
+- Số token đầu vào (Input Tokens): 120 token — đại diện bởi trường `prompt_tokens`, tương ứng với toàn bộ các token trong tin nhắn hệ thống, ngữ cảnh và câu hỏi của người dùng.
+- Số token đầu ra (Output / Generated Tokens): 30 token — đại diện bởi trường `completion_tokens`, tương ứng với số lượng token mà mô hình đã sinh ra trong câu trả lời.
+- Tổng số token (Total Tokens): 150 token — đại diện bởi trường `total_tokens`, là tổng cộng lượng tài nguyên token đã tiêu thụ trong lần gọi API này ($120 + 30 = 150$ token).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Việc phân định rạch ròi giữa `prompt_tokens` và `completion_tokens` là cốt lõi trong hạch toán chi phí LLM, vì hầu hết các nhà cung cấp áp dụng đơn giá cho token đầu ra đắt gấp 2 đến 4 lần so với token đầu vào.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI API Reference - Chat Completion Object Usage (https://platform.openai.com/docs/api-reference/chat/object#chat/object-usage)</t>
         </is>
       </c>
     </row>
